--- a/Agentes/Maria/Sistemas de RH/Relatórios/2026-09/Radar Diário do Ponto - 2026-09-30.xlsx
+++ b/Agentes/Maria/Sistemas de RH/Relatórios/2026-09/Radar Diário do Ponto - 2026-09-30.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01/10/2026 07:49:30 BRT</t>
+          <t>01/10/2026 07:50:34 BRT</t>
         </is>
       </c>
     </row>

--- a/Agentes/Maria/Sistemas de RH/Relatórios/2026-09/Radar Diário do Ponto - 2026-09-30.xlsx
+++ b/Agentes/Maria/Sistemas de RH/Relatórios/2026-09/Radar Diário do Ponto - 2026-09-30.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01/10/2026 07:50:34 BRT</t>
+          <t>01/10/2026 07:50:53 BRT</t>
         </is>
       </c>
     </row>
